--- a/docs/downloads/04/tbl_other_act_all_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_other_act_all_marovoay_tous.xlsx
@@ -387,12 +387,6 @@
           <t>Autres activités libérales - Asa mahaleo-tena hafa</t>
         </is>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -423,12 +417,6 @@
           <t>Couturier, tailleur - Mpanjaitra</t>
         </is>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -459,12 +447,6 @@
           <t>Docker, manutentionnaire, porteur - Mpibata entana, Mpanao kibaroa</t>
         </is>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -477,12 +459,6 @@
           <t>Démarcheur de bétail-Mpanao dabokandro</t>
         </is>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -495,12 +471,6 @@
           <t>Eleveur - Mpiompy</t>
         </is>
       </c>
-      <c r="C8">
-        <v>4</v>
-      </c>
-      <c r="D8">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -531,12 +501,6 @@
           <t>Employé permanent d?un ménage et membre de ce ménage ? Mpiasa raikitra ao @ tokantrano iray sady mipetraka ao aminy</t>
         </is>
       </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -549,12 +513,6 @@
           <t>Gardien de bétail (Salarié) - Mpikarama miandry omby</t>
         </is>
       </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -567,12 +525,6 @@
           <t>Gargotier - Mpivarotra hani-masaka</t>
         </is>
       </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -603,12 +555,6 @@
           <t>Man?uvre ou ouvrier (entreprise et société) - ) - Mpanampy @ taotrano</t>
         </is>
       </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -621,12 +567,6 @@
           <t>Membre d?un ménage mais employé permanent chez un autre ménage ? Olona mpikambana ao @ tokantrano iray fa mpiasa raikitra any @ tokantrano hafa</t>
         </is>
       </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -657,12 +597,6 @@
           <t>Producteur de toaka gasy, de betsa - Mpamboatra toaka gasy, betsa</t>
         </is>
       </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -675,12 +609,6 @@
           <t>Pêcheur exploitant- Mpanjono miasa tena</t>
         </is>
       </c>
-      <c r="C18">
-        <v>3</v>
-      </c>
-      <c r="D18">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -693,12 +621,6 @@
           <t>Retraité - Misotro ronono, mandray fisotroan-dronono</t>
         </is>
       </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -711,12 +633,6 @@
           <t>Sage-femme, infirmier - Mpampivelona, mpitsabo mpanampy</t>
         </is>
       </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -742,12 +658,6 @@
           <t>Aide Sanitaire</t>
         </is>
       </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -760,12 +670,6 @@
           <t>Animateur rural, alphabétiseur ? Mpanentana eny ambanivohitra, Mpampianatra mamaky teny sy manoratra</t>
         </is>
       </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -778,12 +682,6 @@
           <t>Collecteur (riz) - Mpanangom-bary</t>
         </is>
       </c>
-      <c r="C24">
-        <v>2</v>
-      </c>
-      <c r="D24">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -832,12 +730,6 @@
           <t>Démarcheur et Kinanga autre que produit de pêche - Mpanelanelana sy kinanga amin?ny vokatra hafa ankoatra ny jono</t>
         </is>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -868,12 +760,6 @@
           <t>Employé permanent d?un ménage et membre de ce ménage ? Mpiasa raikitra ao @ tokantrano iray sady mipetraka ao aminy</t>
         </is>
       </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -886,12 +772,6 @@
           <t>Enseignant du primaire - Mpampianatra @ fanabeazana fototra</t>
         </is>
       </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -904,12 +784,6 @@
           <t>Exploitant minier, prospecteur de pierres et métaux précieux (rubis, saphir, or...) - Mpitrandraka vato, na vy sarobidy</t>
         </is>
       </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="D31">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -922,12 +796,6 @@
           <t>Gargotier - Mpivarotra hani-masaka</t>
         </is>
       </c>
-      <c r="C32">
-        <v>4</v>
-      </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -976,12 +844,6 @@
           <t>Porteur d'eau - Mpaka rano</t>
         </is>
       </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -994,12 +856,6 @@
           <t>Pêcheur exploitant- Mpanjono miasa tena</t>
         </is>
       </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1012,12 +868,6 @@
           <t>Retraité - Misotro ronono, mandray fisotroan-dronono</t>
         </is>
       </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1043,12 +893,6 @@
           <t>Artisan NCA (exerçant un métier manuel à son propre compte) - Mpanao asa tanana tsy voasokajy teo aloha miasa tena</t>
         </is>
       </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1061,12 +905,6 @@
           <t>Commerçant, épicier, vendeur - Mpivarotra</t>
         </is>
       </c>
-      <c r="C40">
-        <v>3</v>
-      </c>
-      <c r="D40">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1097,12 +935,6 @@
           <t>Eleveur - Mpiompy</t>
         </is>
       </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-      <c r="D42">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1133,12 +965,6 @@
           <t>Exploitantforestier, bûcheron, charbonnier- Mpitrandraka ala, mpamaky kitay, mpanao arina</t>
         </is>
       </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-      <c r="D44">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1151,12 +977,6 @@
           <t>Fournisseur de matières premières pour les matériaux de construction - Mpamatsy akora @ fanamboarana trano -</t>
         </is>
       </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-      <c r="D45">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1205,12 +1025,6 @@
           <t>Ouvrier d'entretien, bricoleur (kibaroa) - Kibaroa, manao izay asa hita</t>
         </is>
       </c>
-      <c r="C48">
-        <v>3</v>
-      </c>
-      <c r="D48">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1254,12 +1068,6 @@
           <t>Activités domestiques - Asa an-trano</t>
         </is>
       </c>
-      <c r="C51">
-        <v>2</v>
-      </c>
-      <c r="D51">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1272,12 +1080,6 @@
           <t>Barman, serveur - Mpiasa @ trano fisotroana, mpandroso sakafo</t>
         </is>
       </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-      <c r="D52">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1308,12 +1110,6 @@
           <t>Conducteur de véhicule, engin, transporteur camion et voiture - Mpamily fiara, Mpitatitra @ fiara, fiarabe?</t>
         </is>
       </c>
-      <c r="C54">
-        <v>1</v>
-      </c>
-      <c r="D54">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1344,12 +1140,6 @@
           <t>Démarcheur et Kinanga autre que produit de pêche - Mpanelanelana sy kinanga amin?ny vokatra hafa ankoatra ny jono</t>
         </is>
       </c>
-      <c r="C56">
-        <v>1</v>
-      </c>
-      <c r="D56">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1362,12 +1152,6 @@
           <t>Eleveur - Mpiompy</t>
         </is>
       </c>
-      <c r="C57">
-        <v>2</v>
-      </c>
-      <c r="D57">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1398,12 +1182,6 @@
           <t>Employé du secteur tertiaire (commerce, administration, service) : gérant, agent, secrétaire, caissier, vendeur, comptable, aide-comptable,... - Mpiasa amin?ny fandraharahana momba ny varotra, mpitantsoratra, mpandray vola, mpitantambola na ny mpanampy az</t>
         </is>
       </c>
-      <c r="C59">
-        <v>1</v>
-      </c>
-      <c r="D59">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1416,12 +1194,6 @@
           <t>Employé permanent d?un ménage et membre de ce ménage ? Mpiasa raikitra ao @ tokantrano iray sady mipetraka ao aminy</t>
         </is>
       </c>
-      <c r="C60">
-        <v>1</v>
-      </c>
-      <c r="D60">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1434,12 +1206,6 @@
           <t>Enseignant du secondaire - Mpampianatra @ Ambaratonga faharoa</t>
         </is>
       </c>
-      <c r="C61">
-        <v>1</v>
-      </c>
-      <c r="D61">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1452,12 +1218,6 @@
           <t>Gardien de bétail (Salarié) - Mpikarama miandry omby</t>
         </is>
       </c>
-      <c r="C62">
-        <v>1</v>
-      </c>
-      <c r="D62">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1506,12 +1266,6 @@
           <t>Machiniste, ajusteur, tourneur, fraiseur, rectificateur, soudeur, mécanicien - Mpanao asa momba ny vy</t>
         </is>
       </c>
-      <c r="C65">
-        <v>2</v>
-      </c>
-      <c r="D65">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1524,12 +1278,6 @@
           <t>Maçon, Ouvrier du bâtiment, peintre en bâtiment, Plombier - Mpandalotra, Mpiasa @ taotrano, Mpiasa mikarakara ny rano</t>
         </is>
       </c>
-      <c r="C66">
-        <v>2</v>
-      </c>
-      <c r="D66">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1542,12 +1290,6 @@
           <t>Menuisier, charpentier, Ebéniste, Sculpteur - Mpandrafitra hazo, trano, Mpanao sary sokitra</t>
         </is>
       </c>
-      <c r="C67">
-        <v>1</v>
-      </c>
-      <c r="D67">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1560,12 +1302,6 @@
           <t>Mécanicien- Mpanamboatra fiarakodia</t>
         </is>
       </c>
-      <c r="C68">
-        <v>1</v>
-      </c>
-      <c r="D68">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1596,12 +1332,6 @@
           <t>Piroguier - Mpivoy lakana</t>
         </is>
       </c>
-      <c r="C70">
-        <v>1</v>
-      </c>
-      <c r="D70">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1614,12 +1344,6 @@
           <t>Porteur d'eau - Mpaka rano</t>
         </is>
       </c>
-      <c r="C71">
-        <v>1</v>
-      </c>
-      <c r="D71">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1632,12 +1356,6 @@
           <t>Pêcheur exploitant- Mpanjono miasa tena</t>
         </is>
       </c>
-      <c r="C72">
-        <v>2</v>
-      </c>
-      <c r="D72">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1650,12 +1368,6 @@
           <t>Sage-femme, infirmier - Mpampivelona, mpitsabo mpanampy</t>
         </is>
       </c>
-      <c r="C73">
-        <v>1</v>
-      </c>
-      <c r="D73">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1668,12 +1380,6 @@
           <t>Tisseur (Mpandrary) avec des brins végétaux (nattes, soubiques,chapeaux...),tresseur(vannerie),Fileur (sisalerie) - Mpandrary tsihy, sobika, satroka, tsihy, mpanao tady</t>
         </is>
       </c>
-      <c r="C74">
-        <v>1</v>
-      </c>
-      <c r="D74">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1699,12 +1405,6 @@
           <t>Activités domestiques - Asa an-trano</t>
         </is>
       </c>
-      <c r="C76">
-        <v>2</v>
-      </c>
-      <c r="D76">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1717,12 +1417,6 @@
           <t>Aide Sanitaire</t>
         </is>
       </c>
-      <c r="C77">
-        <v>1</v>
-      </c>
-      <c r="D77">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1735,12 +1429,6 @@
           <t>Animateur rural, alphabétiseur ? Mpanentana eny ambanivohitra, Mpampianatra mamaky teny sy manoratra</t>
         </is>
       </c>
-      <c r="C78">
-        <v>1</v>
-      </c>
-      <c r="D78">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1753,12 +1441,6 @@
           <t>Artisan NCA (exerçant un métier manuel à son propre compte) - Mpanao asa tanana tsy voasokajy teo aloha miasa tena</t>
         </is>
       </c>
-      <c r="C79">
-        <v>1</v>
-      </c>
-      <c r="D79">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1771,12 +1453,6 @@
           <t>Autres activités libérales - Asa mahaleo-tena hafa</t>
         </is>
       </c>
-      <c r="C80">
-        <v>1</v>
-      </c>
-      <c r="D80">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1789,12 +1465,6 @@
           <t>Barman, serveur - Mpiasa @ trano fisotroana, mpandroso sakafo</t>
         </is>
       </c>
-      <c r="C81">
-        <v>1</v>
-      </c>
-      <c r="D81">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1807,12 +1477,6 @@
           <t>Collecteur (riz) - Mpanangom-bary</t>
         </is>
       </c>
-      <c r="C82">
-        <v>2</v>
-      </c>
-      <c r="D82">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1843,12 +1507,6 @@
           <t>Conducteur de véhicule, engin, transporteur camion et voiture - Mpamily fiara, Mpitatitra @ fiara, fiarabe?</t>
         </is>
       </c>
-      <c r="C84">
-        <v>1</v>
-      </c>
-      <c r="D84">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1861,12 +1519,6 @@
           <t>Couturier, tailleur - Mpanjaitra</t>
         </is>
       </c>
-      <c r="C85">
-        <v>1</v>
-      </c>
-      <c r="D85">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1897,12 +1549,6 @@
           <t>Docker, manutentionnaire, porteur - Mpibata entana, Mpanao kibaroa</t>
         </is>
       </c>
-      <c r="C87">
-        <v>1</v>
-      </c>
-      <c r="D87">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1915,12 +1561,6 @@
           <t>Démarcheur de bétail-Mpanao dabokandro</t>
         </is>
       </c>
-      <c r="C88">
-        <v>1</v>
-      </c>
-      <c r="D88">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1933,12 +1573,6 @@
           <t>Démarcheur et Kinanga autre que produit de pêche - Mpanelanelana sy kinanga amin?ny vokatra hafa ankoatra ny jono</t>
         </is>
       </c>
-      <c r="C89">
-        <v>2</v>
-      </c>
-      <c r="D89">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1987,12 +1621,6 @@
           <t>Employé du secteur tertiaire (commerce, administration, service) : gérant, agent, secrétaire, caissier, vendeur, comptable, aide-comptable,... - Mpiasa amin?ny fandraharahana momba ny varotra, mpitantsoratra, mpandray vola, mpitantambola na ny mpanampy az</t>
         </is>
       </c>
-      <c r="C92">
-        <v>1</v>
-      </c>
-      <c r="D92">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2023,12 +1651,6 @@
           <t>Enseignant du primaire - Mpampianatra @ fanabeazana fototra</t>
         </is>
       </c>
-      <c r="C94">
-        <v>1</v>
-      </c>
-      <c r="D94">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2041,12 +1663,6 @@
           <t>Enseignant du secondaire - Mpampianatra @ Ambaratonga faharoa</t>
         </is>
       </c>
-      <c r="C95">
-        <v>1</v>
-      </c>
-      <c r="D95">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2059,12 +1675,6 @@
           <t>Exploitant minier, prospecteur de pierres et métaux précieux (rubis, saphir, or...) - Mpitrandraka vato, na vy sarobidy</t>
         </is>
       </c>
-      <c r="C96">
-        <v>1</v>
-      </c>
-      <c r="D96">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2077,12 +1687,6 @@
           <t>Exploitantforestier, bûcheron, charbonnier- Mpitrandraka ala, mpamaky kitay, mpanao arina</t>
         </is>
       </c>
-      <c r="C97">
-        <v>1</v>
-      </c>
-      <c r="D97">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2095,12 +1699,6 @@
           <t>Fournisseur de matières premières pour les matériaux de construction - Mpamatsy akora @ fanamboarana trano -</t>
         </is>
       </c>
-      <c r="C98">
-        <v>1</v>
-      </c>
-      <c r="D98">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2113,12 +1711,6 @@
           <t>Gardien de bétail (Salarié) - Mpikarama miandry omby</t>
         </is>
       </c>
-      <c r="C99">
-        <v>2</v>
-      </c>
-      <c r="D99">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2167,12 +1759,6 @@
           <t>Machiniste, ajusteur, tourneur, fraiseur, rectificateur, soudeur, mécanicien - Mpanao asa momba ny vy</t>
         </is>
       </c>
-      <c r="C102">
-        <v>2</v>
-      </c>
-      <c r="D102">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2185,12 +1771,6 @@
           <t>Man?uvre ou ouvrier (entreprise et société) - ) - Mpanampy @ taotrano</t>
         </is>
       </c>
-      <c r="C103">
-        <v>1</v>
-      </c>
-      <c r="D103">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2203,12 +1783,6 @@
           <t>Maçon, Ouvrier du bâtiment, peintre en bâtiment, Plombier - Mpandalotra, Mpiasa @ taotrano, Mpiasa mikarakara ny rano</t>
         </is>
       </c>
-      <c r="C104">
-        <v>2</v>
-      </c>
-      <c r="D104">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2221,12 +1795,6 @@
           <t>Membre d?un ménage mais employé permanent chez un autre ménage ? Olona mpikambana ao @ tokantrano iray fa mpiasa raikitra any @ tokantrano hafa</t>
         </is>
       </c>
-      <c r="C105">
-        <v>1</v>
-      </c>
-      <c r="D105">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2239,12 +1807,6 @@
           <t>Menuisier, charpentier, Ebéniste, Sculpteur - Mpandrafitra hazo, trano, Mpanao sary sokitra</t>
         </is>
       </c>
-      <c r="C106">
-        <v>1</v>
-      </c>
-      <c r="D106">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2257,12 +1819,6 @@
           <t>Mécanicien- Mpanamboatra fiarakodia</t>
         </is>
       </c>
-      <c r="C107">
-        <v>1</v>
-      </c>
-      <c r="D107">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2293,12 +1849,6 @@
           <t>Ouvrier d'entretien, bricoleur (kibaroa) - Kibaroa, manao izay asa hita</t>
         </is>
       </c>
-      <c r="C109">
-        <v>3</v>
-      </c>
-      <c r="D109">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2311,12 +1861,6 @@
           <t>Piroguier - Mpivoy lakana</t>
         </is>
       </c>
-      <c r="C110">
-        <v>1</v>
-      </c>
-      <c r="D110">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2329,12 +1873,6 @@
           <t>Porteur d'eau - Mpaka rano</t>
         </is>
       </c>
-      <c r="C111">
-        <v>2</v>
-      </c>
-      <c r="D111">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2347,12 +1885,6 @@
           <t>Producteur de toaka gasy, de betsa - Mpamboatra toaka gasy, betsa</t>
         </is>
       </c>
-      <c r="C112">
-        <v>1</v>
-      </c>
-      <c r="D112">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2383,12 +1915,6 @@
           <t>Retraité - Misotro ronono, mandray fisotroan-dronono</t>
         </is>
       </c>
-      <c r="C114">
-        <v>2</v>
-      </c>
-      <c r="D114">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2400,12 +1926,6 @@
         <is>
           <t>Sage-femme, infirmier - Mpampivelona, mpitsabo mpanampy</t>
         </is>
-      </c>
-      <c r="C115">
-        <v>2</v>
-      </c>
-      <c r="D115">
-        <v>0.1</v>
       </c>
     </row>
     <row r="116">
